--- a/design_issues/codescene/P8_SocialApp.xlsx
+++ b/design_issues/codescene/P8_SocialApp.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\AI IDE Analysis\AI-IDEs-code-analysis\design_issues\codescene\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DIinAGP\DIinAGP\design_issues\codescene\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Issues" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="107">
   <si>
     <t>resource</t>
   </si>
@@ -119,12 +119,6 @@
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/projects/P8_SocialApp/backend/src/main/java/com/socialapp/util/JwtUtil.java</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments</t>
-  </si>
-  <si>
-    <t>String Heavy Function Arguments ()</t>
   </si>
   <si>
     <t>/E:/AI IDE Analysis/AI-IDEs-code-analysis/projects/P8_SocialApp/frontend/src/components/Button.js</t>
@@ -723,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="127.90625" customWidth="1"/>
@@ -1517,19 +1511,19 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>34</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -1537,163 +1531,163 @@
         <v>35</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>132</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D49">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D52">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E52">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D53">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E53">
-        <v>83</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D54">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E54">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" t="s">
         <v>40</v>
       </c>
-      <c r="B55" t="s">
-        <v>29</v>
-      </c>
-      <c r="C55" t="s">
-        <v>30</v>
-      </c>
       <c r="D55">
-        <v>118</v>
+        <v>339</v>
       </c>
       <c r="E55">
-        <v>118</v>
+        <v>339</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56">
         <v>38</v>
       </c>
-      <c r="C56" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56">
-        <v>339</v>
-      </c>
       <c r="E56">
-        <v>339</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D57">
         <v>38</v>
@@ -1707,27 +1701,27 @@
         <v>43</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D58">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E58">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B59" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D59">
         <v>17</v>
@@ -1747,21 +1741,21 @@
         <v>46</v>
       </c>
       <c r="D60">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E60">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" t="s">
         <v>47</v>
-      </c>
-      <c r="B61" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" t="s">
-        <v>48</v>
       </c>
       <c r="D61">
         <v>8</v>
@@ -1772,53 +1766,53 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C62" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="E62">
-        <v>8</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D63">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="E63">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="E64">
-        <v>5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -1826,61 +1820,61 @@
         <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D65">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D67">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="E67">
-        <v>14</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D68">
         <v>90</v>
@@ -1891,36 +1885,36 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>51</v>
+      </c>
+      <c r="B69" t="s">
+        <v>36</v>
+      </c>
+      <c r="C69" t="s">
         <v>53</v>
       </c>
-      <c r="B69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C69" t="s">
-        <v>54</v>
-      </c>
       <c r="D69">
-        <v>90</v>
+        <v>336</v>
       </c>
       <c r="E69">
-        <v>90</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B70" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
         <v>55</v>
       </c>
       <c r="D70">
-        <v>336</v>
+        <v>14</v>
       </c>
       <c r="E70">
-        <v>336</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -1931,52 +1925,52 @@
         <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="D71">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E71">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>57</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
         <v>58</v>
       </c>
-      <c r="B72" t="s">
-        <v>12</v>
-      </c>
-      <c r="C72" t="s">
-        <v>36</v>
-      </c>
       <c r="D72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C73" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E73">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B74" t="s">
         <v>29</v>
@@ -1985,55 +1979,55 @@
         <v>30</v>
       </c>
       <c r="D74">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E74">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>57</v>
+      </c>
+      <c r="B75" t="s">
+        <v>36</v>
+      </c>
+      <c r="C75" t="s">
         <v>59</v>
       </c>
-      <c r="B75" t="s">
-        <v>29</v>
-      </c>
-      <c r="C75" t="s">
-        <v>30</v>
-      </c>
       <c r="D75">
-        <v>37</v>
+        <v>355</v>
       </c>
       <c r="E75">
-        <v>37</v>
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B76" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D76">
-        <v>355</v>
+        <v>16</v>
       </c>
       <c r="E76">
-        <v>355</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D77">
         <v>16</v>
@@ -2044,19 +2038,19 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D78">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E78">
-        <v>16</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
@@ -2064,27 +2058,27 @@
         <v>62</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="D79">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="E79">
-        <v>91</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C80" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D80">
         <v>18</v>
@@ -2095,30 +2089,30 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B81" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D81">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="E81">
-        <v>18</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" t="s">
+        <v>36</v>
+      </c>
+      <c r="C82" t="s">
         <v>64</v>
-      </c>
-      <c r="B82" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" t="s">
-        <v>36</v>
       </c>
       <c r="D82">
         <v>119</v>
@@ -2129,53 +2123,53 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B83" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D83">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="E83">
-        <v>119</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D84">
-        <v>213</v>
+        <v>35</v>
       </c>
       <c r="E84">
-        <v>213</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C85" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="E85">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -2183,50 +2177,50 @@
         <v>68</v>
       </c>
       <c r="B86" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D86">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="E86">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
         <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D87">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="E87">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C88" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D88">
-        <v>86</v>
+        <v>239</v>
       </c>
       <c r="E88">
-        <v>86</v>
+        <v>239</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -2234,55 +2228,55 @@
         <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C89" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D89">
-        <v>239</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>239</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D91">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="E91">
-        <v>24</v>
+        <v>122</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B92" t="s">
         <v>29</v>
@@ -2291,38 +2285,38 @@
         <v>30</v>
       </c>
       <c r="D92">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E92">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B93" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D93">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="E93">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" t="s">
+        <v>71</v>
+      </c>
+      <c r="C94" t="s">
         <v>72</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="s">
-        <v>23</v>
       </c>
       <c r="D94">
         <v>187</v>
@@ -2333,13 +2327,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B95" t="s">
+        <v>12</v>
+      </c>
+      <c r="C95" t="s">
         <v>73</v>
-      </c>
-      <c r="C95" t="s">
-        <v>74</v>
       </c>
       <c r="D95">
         <v>187</v>
@@ -2350,98 +2344,98 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B96" t="s">
         <v>12</v>
       </c>
       <c r="C96" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="D96">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="E96">
-        <v>187</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B97" t="s">
         <v>12</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D97">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="E97">
-        <v>234</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="D98">
-        <v>257</v>
+        <v>516</v>
       </c>
       <c r="E98">
-        <v>257</v>
+        <v>516</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C99" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D99">
-        <v>516</v>
+        <v>1</v>
       </c>
       <c r="E99">
-        <v>516</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D101">
         <v>18</v>
@@ -2452,24 +2446,24 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B102" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C102" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D102">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="E102">
-        <v>18</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B103" t="s">
         <v>29</v>
@@ -2478,32 +2472,32 @@
         <v>30</v>
       </c>
       <c r="D103">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E103">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B104" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D104">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E104">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B105" t="s">
         <v>8</v>
@@ -2512,15 +2506,15 @@
         <v>9</v>
       </c>
       <c r="D105">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="E105">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B106" t="s">
         <v>8</v>
@@ -2529,72 +2523,72 @@
         <v>9</v>
       </c>
       <c r="D106">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="E106">
-        <v>114</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C107" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="D107">
-        <v>135</v>
+        <v>286</v>
       </c>
       <c r="E107">
-        <v>135</v>
+        <v>286</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C108" t="s">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D108">
-        <v>286</v>
+        <v>1</v>
       </c>
       <c r="E108">
-        <v>286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B109" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B110" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D110">
         <v>20</v>
@@ -2605,53 +2599,53 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C111" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D111">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="E111">
-        <v>20</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D112">
-        <v>91</v>
+        <v>278</v>
       </c>
       <c r="E112">
-        <v>91</v>
+        <v>278</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
+        <v>77</v>
+      </c>
+      <c r="B113" t="s">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
         <v>78</v>
       </c>
-      <c r="B113" t="s">
-        <v>38</v>
-      </c>
-      <c r="C113" t="s">
-        <v>66</v>
-      </c>
       <c r="D113">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="E113">
-        <v>278</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
@@ -2659,33 +2653,33 @@
         <v>79</v>
       </c>
       <c r="B114" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C114" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D114">
-        <v>232</v>
+        <v>28</v>
       </c>
       <c r="E114">
-        <v>232</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C115" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="D115">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="E115">
-        <v>28</v>
+        <v>177</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
@@ -2693,44 +2687,44 @@
         <v>81</v>
       </c>
       <c r="B116" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C116" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="D116">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>177</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="E117">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B118" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C118" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="D118">
         <v>69</v>
@@ -2741,47 +2735,47 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>81</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
         <v>83</v>
       </c>
-      <c r="B119" t="s">
-        <v>8</v>
-      </c>
-      <c r="C119" t="s">
-        <v>9</v>
-      </c>
       <c r="D119">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="E119">
-        <v>69</v>
+        <v>110</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B120" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C120" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D120">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="E120">
-        <v>110</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B121" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D121">
         <v>209</v>
@@ -2792,7 +2786,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B122" t="s">
         <v>12</v>
@@ -2801,21 +2795,21 @@
         <v>13</v>
       </c>
       <c r="D122">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="E122">
-        <v>209</v>
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D123">
         <v>255</v>
@@ -2826,30 +2820,30 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D124">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E124">
-        <v>255</v>
+        <v>274</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B125" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C125" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D125">
         <v>274</v>
@@ -2860,30 +2854,30 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="D126">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="E126">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C127" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="D127">
         <v>289</v>
@@ -2894,30 +2888,30 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>9</v>
+        <v>82</v>
       </c>
       <c r="D128">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="E128">
-        <v>289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C129" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="D129">
         <v>304</v>
@@ -2928,30 +2922,30 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B130" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C130" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D130">
-        <v>304</v>
+        <v>343</v>
       </c>
       <c r="E130">
-        <v>304</v>
+        <v>343</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C131" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D131">
         <v>343</v>
@@ -2962,47 +2956,47 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B132" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C132" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="D132">
-        <v>343</v>
+        <v>569</v>
       </c>
       <c r="E132">
-        <v>343</v>
+        <v>569</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B133" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C133" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="D133">
-        <v>569</v>
+        <v>16</v>
       </c>
       <c r="E133">
-        <v>569</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D134">
         <v>16</v>
@@ -3013,30 +3007,30 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
+        <v>86</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" t="s">
         <v>87</v>
       </c>
-      <c r="B135" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" t="s">
-        <v>57</v>
-      </c>
       <c r="D135">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E135">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
+        <v>86</v>
+      </c>
+      <c r="B136" t="s">
+        <v>36</v>
+      </c>
+      <c r="C136" t="s">
         <v>88</v>
-      </c>
-      <c r="B136" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" t="s">
-        <v>89</v>
       </c>
       <c r="D136">
         <v>22</v>
@@ -3047,64 +3041,64 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C137" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D137">
-        <v>22</v>
+        <v>252</v>
       </c>
       <c r="E137">
-        <v>22</v>
+        <v>252</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B138" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C138" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="D138">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="E138">
-        <v>252</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B139" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C139" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="E139">
-        <v>1</v>
+        <v>163</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D140">
         <v>163</v>
@@ -3115,19 +3109,19 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C141" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D141">
-        <v>163</v>
+        <v>385</v>
       </c>
       <c r="E141">
-        <v>163</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
@@ -3135,44 +3129,44 @@
         <v>92</v>
       </c>
       <c r="B142" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="D142">
-        <v>385</v>
+        <v>1</v>
       </c>
       <c r="E142">
-        <v>385</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C143" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E143">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B144" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C144" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D144">
         <v>20</v>
@@ -3183,36 +3177,36 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="D145">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="E145">
-        <v>20</v>
+        <v>89</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C146" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="D146">
-        <v>89</v>
+        <v>229</v>
       </c>
       <c r="E146">
-        <v>89</v>
+        <v>229</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
@@ -3220,16 +3214,16 @@
         <v>94</v>
       </c>
       <c r="B147" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C147" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="D147">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="E147">
-        <v>229</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
@@ -3237,21 +3231,21 @@
         <v>96</v>
       </c>
       <c r="B148" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="C148" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="D148">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="E148">
-        <v>118</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B149" t="s">
         <v>8</v>
@@ -3260,15 +3254,15 @@
         <v>9</v>
       </c>
       <c r="D149">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E149">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B150" t="s">
         <v>8</v>
@@ -3277,15 +3271,15 @@
         <v>9</v>
       </c>
       <c r="D150">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E150">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B151" t="s">
         <v>8</v>
@@ -3294,15 +3288,15 @@
         <v>9</v>
       </c>
       <c r="D151">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="E151">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B152" t="s">
         <v>8</v>
@@ -3311,15 +3305,15 @@
         <v>9</v>
       </c>
       <c r="D152">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="E152">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B153" t="s">
         <v>8</v>
@@ -3328,15 +3322,15 @@
         <v>9</v>
       </c>
       <c r="D153">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E153">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B154" t="s">
         <v>8</v>
@@ -3345,15 +3339,15 @@
         <v>9</v>
       </c>
       <c r="D154">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="E154">
-        <v>107</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B155" t="s">
         <v>8</v>
@@ -3362,15 +3356,15 @@
         <v>9</v>
       </c>
       <c r="D155">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E155">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B156" t="s">
         <v>8</v>
@@ -3379,15 +3373,15 @@
         <v>9</v>
       </c>
       <c r="D156">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E156">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B157" t="s">
         <v>8</v>
@@ -3396,15 +3390,15 @@
         <v>9</v>
       </c>
       <c r="D157">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E157">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B158" t="s">
         <v>8</v>
@@ -3413,15 +3407,15 @@
         <v>9</v>
       </c>
       <c r="D158">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E158">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B159" t="s">
         <v>8</v>
@@ -3430,15 +3424,15 @@
         <v>9</v>
       </c>
       <c r="D159">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E159">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B160" t="s">
         <v>8</v>
@@ -3447,15 +3441,15 @@
         <v>9</v>
       </c>
       <c r="D160">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E160">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B161" t="s">
         <v>8</v>
@@ -3464,49 +3458,49 @@
         <v>9</v>
       </c>
       <c r="D161">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E161">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B162" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C162" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D162">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E162">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B163" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C163" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B164" t="s">
         <v>8</v>
@@ -3515,111 +3509,94 @@
         <v>9</v>
       </c>
       <c r="D164">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E164">
-        <v>19</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B165" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C165" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="D165">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E165">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
+        <v>99</v>
+      </c>
+      <c r="B166" t="s">
         <v>100</v>
       </c>
-      <c r="B166" t="s">
-        <v>12</v>
-      </c>
       <c r="C166" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="D166">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="E166">
-        <v>61</v>
+        <v>29</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B167" t="s">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="D167">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E167">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B168" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C168" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D168">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="E168">
-        <v>54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B169" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>104</v>
-      </c>
-      <c r="B170" t="s">
-        <v>12</v>
-      </c>
-      <c r="C170" t="s">
-        <v>84</v>
-      </c>
-      <c r="D170">
-        <v>23</v>
-      </c>
-      <c r="E170">
         <v>23</v>
       </c>
     </row>
@@ -3630,7 +3607,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:D13"/>
+  <dimension ref="A2:D12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36.90625" customWidth="1"/>
@@ -3639,13 +3616,13 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D2" s="2"/>
     </row>
@@ -3657,7 +3634,7 @@
         <v>8</v>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIF(Issues!B2:B170,Stats!B3)</f>
+        <f>COUNTIF(Issues!B2:B169,Stats!B3)</f>
         <v>53</v>
       </c>
       <c r="D3" s="2"/>
@@ -3670,7 +3647,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIF(Issues!B2:B171,Stats!B4)</f>
+        <f>COUNTIF(Issues!B2:B170,Stats!B4)</f>
         <v>12</v>
       </c>
       <c r="D4" s="2"/>
@@ -3683,7 +3660,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIF(Issues!B2:B172,Stats!B5)</f>
+        <f>COUNTIF(Issues!B2:B171,Stats!B5)</f>
         <v>45</v>
       </c>
       <c r="D5" s="2"/>
@@ -3693,10 +3670,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIF(Issues!B5:B173,Stats!B6)</f>
+        <f>COUNTIF(Issues!B5:B172,Stats!B6)</f>
         <v>24</v>
       </c>
       <c r="D6" s="2"/>
@@ -3709,7 +3686,7 @@
         <v>29</v>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIF(Issues!B2:B174,Stats!B7)</f>
+        <f>COUNTIF(Issues!B2:B173,Stats!B7)</f>
         <v>12</v>
       </c>
       <c r="D7" s="2"/>
@@ -3719,10 +3696,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIF(Issues!B2:B177,Stats!B8)</f>
+        <f>COUNTIF(Issues!B2:B176,Stats!B8)</f>
         <v>1</v>
       </c>
       <c r="D8" s="2"/>
@@ -3735,7 +3712,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIF(Issues!B2:B178,Stats!B9)</f>
+        <f>COUNTIF(Issues!B2:B177,Stats!B9)</f>
         <v>14</v>
       </c>
       <c r="D9" s="2"/>
@@ -3748,7 +3725,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIF(Issues!B2:B179,Stats!B10)</f>
+        <f>COUNTIF(Issues!B2:B178,Stats!B10)</f>
         <v>6</v>
       </c>
       <c r="D10" s="2"/>
@@ -3758,7 +3735,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <f>COUNTIF(Issues!B2:B180,Stats!B11)</f>
@@ -3767,28 +3744,15 @@
       <c r="D11" s="2"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="2">
-        <f>COUNTIF(Issues!B2:B181,Stats!B12)</f>
-        <v>1</v>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="3">
+        <f>SUM(C3:C11)</f>
+        <v>168</v>
       </c>
       <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C13" s="3">
-        <f>SUM(C3:C12)</f>
-        <v>169</v>
-      </c>
-      <c r="D13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
